--- a/supplychain_analysis_dashboard.xlsx
+++ b/supplychain_analysis_dashboard.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1957" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1956" uniqueCount="180">
   <si>
     <t>Product type</t>
   </si>
@@ -568,9 +568,6 @@
   </si>
   <si>
     <t>total_costs</t>
-  </si>
-  <si>
-    <t>prfotmargin</t>
   </si>
   <si>
     <t>Sum of net_profit</t>
@@ -2259,7 +2256,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[supplychain_dataanalysis_dashboard.xlsx]shipping cost vs time pivot!PivotTable8</c:name>
+    <c:name>[supplychain_analysis_dashboard.xlsx]shipping cost vs time pivot!PivotTable8</c:name>
     <c:fmtId val="8"/>
   </c:pivotSource>
   <c:chart>
@@ -2708,7 +2705,7 @@
         <c:spPr>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:schemeClr val="accent2"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -2800,7 +2797,7 @@
         <c:spPr>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:schemeClr val="accent2"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -2892,7 +2889,7 @@
         <c:spPr>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:schemeClr val="accent2"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -3652,7 +3649,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[supplychain_dataanalysis_dashboard.xlsx]profitmrg by hub pivot !PivotTable4</c:name>
+    <c:name>[supplychain_analysis_dashboard.xlsx]profitmrg by hub pivot !PivotTable4</c:name>
     <c:fmtId val="3"/>
   </c:pivotSource>
   <c:chart>
@@ -4452,7 +4449,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[supplychain_dataanalysis_dashboard.xlsx]operatinal &amp; quality pivots!PivotTable2</c:name>
+    <c:name>[supplychain_analysis_dashboard.xlsx]operatinal &amp; quality pivots!PivotTable2</c:name>
     <c:fmtId val="3"/>
   </c:pivotSource>
   <c:chart>
@@ -5621,7 +5618,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[supplychain_dataanalysis_dashboard.xlsx]operatinal &amp; quality pivots!PivotTable3</c:name>
+    <c:name>[supplychain_analysis_dashboard.xlsx]operatinal &amp; quality pivots!PivotTable3</c:name>
     <c:fmtId val="3"/>
   </c:pivotSource>
   <c:chart>
@@ -8523,7 +8520,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[supplychain_dataanalysis_dashboard.xlsx]operatinal &amp; quality pivots!PivotTable4</c:name>
+    <c:name>[supplychain_analysis_dashboard.xlsx]operatinal &amp; quality pivots!PivotTable4</c:name>
     <c:fmtId val="3"/>
   </c:pivotSource>
   <c:chart>
@@ -9800,7 +9797,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[supplychain_dataanalysis_dashboard.xlsx]shipping cost vs time pivot!PivotTable8</c:name>
+    <c:name>[supplychain_analysis_dashboard.xlsx]shipping cost vs time pivot!PivotTable8</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -10178,7 +10175,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -10275,12 +10271,11 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[supplychain_dataanalysis_dashboard.xlsx]shipping cost vs time pivot!PivotTable9</c:name>
+    <c:name>[supplychain_analysis_dashboard.xlsx]shipping cost vs time pivot!PivotTable9</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
     <c:title>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -10343,7 +10338,6 @@
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
-          <c:layout/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -10380,9 +10374,7 @@
           <c:showPercent val="1"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:layout/>
-            </c:ext>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -10577,9 +10569,7 @@
               </c:spPr>
             </c:leaderLines>
             <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
-              </c:ext>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
             </c:extLst>
           </c:dLbls>
           <c:cat>
@@ -10650,7 +10640,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -10748,6 +10737,7 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -11638,7 +11628,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[supplychain_dataanalysis_dashboard.xlsx]operatinal &amp; quality pivots!PivotTable2</c:name>
+    <c:name>[supplychain_analysis_dashboard.xlsx]operatinal &amp; quality pivots!PivotTable2</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -11899,7 +11889,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[supplychain_dataanalysis_dashboard.xlsx]operatinal &amp; quality pivots!PivotTable3</c:name>
+    <c:name>[supplychain_analysis_dashboard.xlsx]operatinal &amp; quality pivots!PivotTable3</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -12051,7 +12041,6 @@
                   <a:noFill/>
                 </a:ln>
               </c15:spPr>
-              <c15:layout/>
             </c:ext>
           </c:extLst>
         </c:dLbl>
@@ -12196,7 +12185,6 @@
                   <a:noFill/>
                 </a:ln>
               </c15:spPr>
-              <c15:layout/>
             </c:ext>
           </c:extLst>
         </c:dLbl>
@@ -12266,7 +12254,6 @@
                   <a:noFill/>
                 </a:ln>
               </c15:spPr>
-              <c15:layout/>
             </c:ext>
           </c:extLst>
         </c:dLbl>
@@ -12336,7 +12323,6 @@
                   <a:noFill/>
                 </a:ln>
               </c15:spPr>
-              <c15:layout/>
             </c:ext>
           </c:extLst>
         </c:dLbl>
@@ -12466,9 +12452,7 @@
               <c:showPercent val="1"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000001-2BF2-4216-BA6E-6583C237A2B2}"/>
                 </c:ext>
@@ -12489,9 +12473,7 @@
               <c:showPercent val="1"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000002-2BF2-4216-BA6E-6583C237A2B2}"/>
                 </c:ext>
@@ -12512,9 +12494,7 @@
               <c:showPercent val="1"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000003-2BF2-4216-BA6E-6583C237A2B2}"/>
                 </c:ext>
@@ -12601,9 +12581,7 @@
               <c:showPercent val="1"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
-                </c:ext>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000005-2BF2-4216-BA6E-6583C237A2B2}"/>
                 </c:ext>
@@ -12811,7 +12789,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[supplychain_dataanalysis_dashboard.xlsx]operatinal &amp; quality pivots!PivotTable4</c:name>
+    <c:name>[supplychain_analysis_dashboard.xlsx]operatinal &amp; quality pivots!PivotTable4</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -13093,12 +13071,11 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[supplychain_dataanalysis_dashboard.xlsx]profitmrg by hub pivot !PivotTable4</c:name>
+    <c:name>[supplychain_analysis_dashboard.xlsx]profitmrg by hub pivot !PivotTable4</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
     <c:title>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -13359,7 +13336,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -13456,7 +13432,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[supplychain_dataanalysis_dashboard.xlsx]product perform pivots!PivotTable2</c:name>
+    <c:name>[supplychain_analysis_dashboard.xlsx]product perform pivots!PivotTable2</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -13849,7 +13825,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -14942,7 +14917,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[supplychain_dataanalysis_dashboard.xlsx]product perform pivots!PivotTable2</c:name>
+    <c:name>[supplychain_analysis_dashboard.xlsx]product perform pivots!PivotTable2</c:name>
     <c:fmtId val="3"/>
   </c:pivotSource>
   <c:chart>
@@ -24640,7 +24615,7 @@
               <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
             <a:pPr marL="0" indent="0" algn="ctr"/>
-            <a:t>30%</a:t>
+            <a:t>54%</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="3200" b="0" i="0" u="none" strike="noStrike">
             <a:solidFill>
@@ -25251,7 +25226,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>Executive Supply Chain Performance | Q1 2026</a:t>
+            <a:t>Executive Supply Chain Performance | Q1 2025</a:t>
           </a:r>
           <a:endParaRPr lang="en-US" sz="3200">
             <a:solidFill>
@@ -28796,8 +28771,8 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>113394</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="59" name="Location"/>
@@ -28814,7 +28789,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -28868,8 +28843,8 @@
       <xdr:row>24</xdr:row>
       <xdr:rowOff>45358</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="61" name="Product type"/>
@@ -28886,7 +28861,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -42087,72 +42062,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A57:C74" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="36">
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="2" showAll="0"/>
-    <pivotField numFmtId="2" showAll="0"/>
-    <pivotField numFmtId="2" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12">
   <location ref="A27:C31" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="36">
@@ -42300,7 +42209,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="13">
   <location ref="A2:C19" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="32">
@@ -42340,6 +42249,72 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField numFmtId="2" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A57:C74" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="36">
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -42950,7 +42925,7 @@
         <v>169</v>
       </c>
       <c r="V1" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="W1" s="2" t="s">
         <v>20</v>
@@ -52028,7 +52003,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AG101"/>
+  <dimension ref="A1:AF101"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.54296875" style="6" customWidth="1"/>
@@ -52057,7 +52032,7 @@
     <col min="29" max="29" width="15.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -52131,7 +52106,7 @@
         <v>169</v>
       </c>
       <c r="Y1" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Z1" s="2" t="s">
         <v>20</v>
@@ -52154,11 +52129,8 @@
       <c r="AF1" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="AG1" s="1" t="s">
-        <v>174</v>
-      </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>23</v>
       </c>
@@ -52257,11 +52229,8 @@
       <c r="AF2">
         <v>5187.0852044951553</v>
       </c>
-      <c r="AG2">
-        <v>0.5988325011908161</v>
-      </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>28</v>
       </c>
@@ -52360,11 +52329,8 @@
       <c r="AF3">
         <v>5762.5357157028102</v>
       </c>
-      <c r="AG3">
-        <v>0.7723646832359039</v>
-      </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>23</v>
       </c>
@@ -52463,11 +52429,8 @@
       <c r="AF4">
         <v>6530.8535927765997</v>
       </c>
-      <c r="AG4">
-        <v>0.68187766937833605</v>
-      </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>28</v>
       </c>
@@ -52566,11 +52529,8 @@
       <c r="AF5">
         <v>7057.2350168276353</v>
       </c>
-      <c r="AG5">
-        <v>0.90863700869109132</v>
-      </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>28</v>
       </c>
@@ -52669,11 +52629,8 @@
       <c r="AF6">
         <v>-1119.3643960069448</v>
       </c>
-      <c r="AG6">
-        <v>-0.41666192054530488</v>
-      </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>23</v>
       </c>
@@ -52772,11 +52729,8 @@
       <c r="AF7">
         <v>-2122.0436165533047</v>
       </c>
-      <c r="AG7">
-        <v>-0.75027650659155987</v>
-      </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>28</v>
       </c>
@@ -52875,11 +52829,8 @@
       <c r="AF8">
         <v>6977.1175526078005</v>
       </c>
-      <c r="AG8">
-        <v>0.89181804272260923</v>
-      </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>42</v>
       </c>
@@ -52978,11 +52929,8 @@
       <c r="AF9">
         <v>5481.6113188979152</v>
       </c>
-      <c r="AG9">
-        <v>0.64519118874847925</v>
-      </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>42</v>
       </c>
@@ -53081,11 +53029,8 @@
       <c r="AF10">
         <v>6997.7819708276002</v>
       </c>
-      <c r="AG10">
-        <v>0.93088251488650653</v>
-      </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>28</v>
       </c>
@@ -53184,11 +53129,8 @@
       <c r="AF11">
         <v>2003.7446939822948</v>
       </c>
-      <c r="AG11">
-        <v>0.40307500503631344</v>
-      </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>28</v>
       </c>
@@ -53287,11 +53229,8 @@
       <c r="AF12">
         <v>1277.25075727071</v>
       </c>
-      <c r="AG12">
-        <v>0.54794916172705455</v>
-      </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>28</v>
       </c>
@@ -53390,11 +53329,8 @@
       <c r="AF13">
         <v>3548.1541134138351</v>
       </c>
-      <c r="AG13">
-        <v>0.58166993765575226</v>
-      </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>23</v>
       </c>
@@ -53493,11 +53429,8 @@
       <c r="AF14">
         <v>-919.88241699324999</v>
       </c>
-      <c r="AG14">
-        <v>-0.32009922753029296</v>
-      </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
         <v>28</v>
       </c>
@@ -53596,11 +53529,8 @@
       <c r="AF15">
         <v>1901.8929313621798</v>
       </c>
-      <c r="AG15">
-        <v>0.46928588426580442</v>
-      </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
         <v>28</v>
       </c>
@@ -53699,11 +53629,8 @@
       <c r="AF16">
         <v>7671.9236959077398</v>
       </c>
-      <c r="AG16">
-        <v>0.88656160111204863</v>
-      </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
         <v>28</v>
       </c>
@@ -53802,11 +53729,8 @@
       <c r="AF17">
         <v>795.91033559322477</v>
       </c>
-      <c r="AG17">
-        <v>0.14625094508393902</v>
-      </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
         <v>28</v>
       </c>
@@ -53905,11 +53829,8 @@
       <c r="AF18">
         <v>5515.0375908802653</v>
       </c>
-      <c r="AG18">
-        <v>0.85454140617276086</v>
-      </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
         <v>42</v>
       </c>
@@ -54008,11 +53929,8 @@
       <c r="AF19">
         <v>-1584.0377151779448</v>
       </c>
-      <c r="AG19">
-        <v>-0.60243396324189713</v>
-      </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
         <v>23</v>
       </c>
@@ -54111,11 +54029,8 @@
       <c r="AF20">
         <v>5425.7742526044512</v>
       </c>
-      <c r="AG20">
-        <v>0.57938744470518722</v>
-      </c>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>28</v>
       </c>
@@ -54214,11 +54129,8 @@
       <c r="AF21">
         <v>-1857.4987327439953</v>
       </c>
-      <c r="AG21">
-        <v>-0.72743369663996882</v>
-      </c>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
         <v>28</v>
       </c>
@@ -54317,11 +54229,8 @@
       <c r="AF22">
         <v>4271.9022734454047</v>
       </c>
-      <c r="AG22">
-        <v>0.52557673678946071</v>
-      </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
         <v>42</v>
       </c>
@@ -54420,11 +54329,8 @@
       <c r="AF23">
         <v>3076.7711372696403</v>
       </c>
-      <c r="AG23">
-        <v>0.43413972903729425</v>
-      </c>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
         <v>23</v>
       </c>
@@ -54523,11 +54429,8 @@
       <c r="AF24">
         <v>-388.48765180254486</v>
       </c>
-      <c r="AG24">
-        <v>-0.16249220911345769</v>
-      </c>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
         <v>42</v>
       </c>
@@ -54626,11 +54529,8 @@
       <c r="AF25">
         <v>6889.1508281193455</v>
       </c>
-      <c r="AG25">
-        <v>0.77769981578363401</v>
-      </c>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
         <v>23</v>
       </c>
@@ -54729,11 +54629,8 @@
       <c r="AF26">
         <v>5224.4009812363493</v>
       </c>
-      <c r="AG26">
-        <v>0.57734070382876701</v>
-      </c>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
         <v>23</v>
       </c>
@@ -54832,11 +54729,8 @@
       <c r="AF27">
         <v>-1578.9121489907002</v>
       </c>
-      <c r="AG27">
-        <v>-0.72601103907735298</v>
-      </c>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
         <v>23</v>
       </c>
@@ -54935,11 +54829,8 @@
       <c r="AF28">
         <v>1690.6579864497551</v>
       </c>
-      <c r="AG28">
-        <v>0.45490677318599915</v>
-      </c>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
         <v>42</v>
       </c>
@@ -55038,11 +54929,8 @@
       <c r="AF29">
         <v>217.10114699495534</v>
       </c>
-      <c r="AG29">
-        <v>8.0813178445465442E-2</v>
-      </c>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
         <v>42</v>
       </c>
@@ -55141,11 +55029,8 @@
       <c r="AF30">
         <v>4432.8737724841048</v>
       </c>
-      <c r="AG30">
-        <v>0.72464256049999443</v>
-      </c>
     </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
         <v>42</v>
       </c>
@@ -55244,11 +55129,8 @@
       <c r="AF31">
         <v>3986.5391939688861</v>
       </c>
-      <c r="AG31">
-        <v>0.47921451911454099</v>
-      </c>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
         <v>23</v>
       </c>
@@ -55347,11 +55229,8 @@
       <c r="AF32">
         <v>1008.8212701908899</v>
       </c>
-      <c r="AG32">
-        <v>0.36467694030719644</v>
-      </c>
     </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
         <v>28</v>
       </c>
@@ -55450,11 +55329,8 @@
       <c r="AF33">
         <v>5421.8088177859208</v>
       </c>
-      <c r="AG33">
-        <v>0.56154665471836396</v>
-      </c>
     </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
         <v>28</v>
       </c>
@@ -55553,11 +55429,8 @@
       <c r="AF34">
         <v>8899.7050030226546</v>
       </c>
-      <c r="AG34">
-        <v>0.92980808227521339</v>
-      </c>
     </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A35" s="5" t="s">
         <v>42</v>
       </c>
@@ -55656,11 +55529,8 @@
       <c r="AF35">
         <v>3876.1175543116001</v>
       </c>
-      <c r="AG35">
-        <v>0.7526444263820975</v>
-      </c>
     </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
         <v>28</v>
       </c>
@@ -55759,11 +55629,8 @@
       <c r="AF36">
         <v>8118.0001897624397</v>
       </c>
-      <c r="AG36">
-        <v>0.89585733680677027</v>
-      </c>
     </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A37" s="5" t="s">
         <v>42</v>
       </c>
@@ -55862,11 +55729,8 @@
       <c r="AF37">
         <v>4522.2844735615599</v>
       </c>
-      <c r="AG37">
-        <v>0.6913402819496971</v>
-      </c>
     </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A38" s="5" t="s">
         <v>28</v>
       </c>
@@ -55965,11 +55829,8 @@
       <c r="AF38">
         <v>5045.6167867214099</v>
       </c>
-      <c r="AG38">
-        <v>0.66622853001722659</v>
-      </c>
     </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A39" s="5" t="s">
         <v>28</v>
       </c>
@@ -56068,11 +55929,8 @@
       <c r="AF39">
         <v>-76.987965278325191</v>
       </c>
-      <c r="AG39">
-        <v>-3.1573926307922461E-2</v>
-      </c>
     </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A40" s="5" t="s">
         <v>42</v>
       </c>
@@ -56171,11 +56029,8 @@
       <c r="AF40">
         <v>5849.05847044658</v>
       </c>
-      <c r="AG40">
-        <v>0.60347364233982193</v>
-      </c>
     </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A41" s="5" t="s">
         <v>28</v>
       </c>
@@ -56274,11 +56129,8 @@
       <c r="AF41">
         <v>-1981.855543782475</v>
       </c>
-      <c r="AG41">
-        <v>-1.0362829419740851</v>
-      </c>
     </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A42" s="5" t="s">
         <v>28</v>
       </c>
@@ -56377,11 +56229,8 @@
       <c r="AF42">
         <v>2672.6930023601253</v>
       </c>
-      <c r="AG42">
-        <v>0.46684925407323996</v>
-      </c>
     </row>
-    <row r="43" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A43" s="5" t="s">
         <v>28</v>
       </c>
@@ -56480,11 +56329,8 @@
       <c r="AF43">
         <v>2613.1934837580397</v>
       </c>
-      <c r="AG43">
-        <v>0.47330127411820749</v>
-      </c>
     </row>
-    <row r="44" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A44" s="5" t="s">
         <v>28</v>
       </c>
@@ -56583,11 +56429,8 @@
       <c r="AF44">
         <v>-777.19514774402978</v>
       </c>
-      <c r="AG44">
-        <v>-0.42247834612070834</v>
-      </c>
     </row>
-    <row r="45" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A45" s="5" t="s">
         <v>23</v>
       </c>
@@ -56686,11 +56529,8 @@
       <c r="AF45">
         <v>4821.0611053754656</v>
       </c>
-      <c r="AG45">
-        <v>0.84028298443046268</v>
-      </c>
     </row>
-    <row r="46" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A46" s="5" t="s">
         <v>42</v>
       </c>
@@ -56789,11 +56629,8 @@
       <c r="AF46">
         <v>6330.4534082184146</v>
       </c>
-      <c r="AG46">
-        <v>0.8850951100757557</v>
-      </c>
     </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A47" s="5" t="s">
         <v>23</v>
       </c>
@@ -56892,11 +56729,8 @@
       <c r="AF47">
         <v>2500.8544513587449</v>
       </c>
-      <c r="AG47">
-        <v>0.47472949052909463</v>
-      </c>
     </row>
-    <row r="48" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A48" s="5" t="s">
         <v>23</v>
       </c>
@@ -56995,11 +56829,8 @@
       <c r="AF48">
         <v>-1770.8615382226099</v>
       </c>
-      <c r="AG48">
-        <v>-0.69261739080702844</v>
-      </c>
     </row>
-    <row r="49" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A49" s="5" t="s">
         <v>28</v>
       </c>
@@ -57098,11 +56929,8 @@
       <c r="AF49">
         <v>6455.8590828871447</v>
       </c>
-      <c r="AG49">
-        <v>0.91062593011704385</v>
-      </c>
     </row>
-    <row r="50" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A50" s="5" t="s">
         <v>23</v>
       </c>
@@ -57201,11 +57029,8 @@
       <c r="AF50">
         <v>3326.7210216762455</v>
       </c>
-      <c r="AG50">
-        <v>0.44973490447952041</v>
-      </c>
     </row>
-    <row r="51" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A51" s="5" t="s">
         <v>42</v>
       </c>
@@ -57304,11 +57129,8 @@
       <c r="AF51">
         <v>7384.4280689598654</v>
       </c>
-      <c r="AG51">
-        <v>0.92286741165440145</v>
-      </c>
     </row>
-    <row r="52" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A52" s="5" t="s">
         <v>42</v>
       </c>
@@ -57407,11 +57229,8 @@
       <c r="AF52">
         <v>3323.3855200235894</v>
       </c>
-      <c r="AG52">
-        <v>0.56224834367999066</v>
-      </c>
     </row>
-    <row r="53" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A53" s="5" t="s">
         <v>23</v>
       </c>
@@ -57510,11 +57329,8 @@
       <c r="AF53">
         <v>7385.2222065199894</v>
       </c>
-      <c r="AG53">
-        <v>0.74851751500807739</v>
-      </c>
     </row>
-    <row r="54" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A54" s="5" t="s">
         <v>28</v>
       </c>
@@ -57613,11 +57429,8 @@
       <c r="AF54">
         <v>5855.5420101154295</v>
       </c>
-      <c r="AG54">
-        <v>0.6205690258236084</v>
-      </c>
     </row>
-    <row r="55" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A55" s="5" t="s">
         <v>28</v>
       </c>
@@ -57716,11 +57529,8 @@
       <c r="AF55">
         <v>5583.2912095223646</v>
       </c>
-      <c r="AG55">
-        <v>0.67821478659557666</v>
-      </c>
     </row>
-    <row r="56" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A56" s="5" t="s">
         <v>23</v>
       </c>
@@ -57819,11 +57629,8 @@
       <c r="AF56">
         <v>4380.2581960247353</v>
       </c>
-      <c r="AG56">
-        <v>0.71948796673222193</v>
-      </c>
     </row>
-    <row r="57" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A57" s="5" t="s">
         <v>23</v>
       </c>
@@ -57922,11 +57729,8 @@
       <c r="AF57">
         <v>1548.0533146472649</v>
       </c>
-      <c r="AG57">
-        <v>0.52912685945463689</v>
-      </c>
     </row>
-    <row r="58" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A58" s="5" t="s">
         <v>28</v>
       </c>
@@ -58025,11 +57829,8 @@
       <c r="AF58">
         <v>4127.711484336005</v>
       </c>
-      <c r="AG58">
-        <v>0.86588918547597049</v>
-      </c>
     </row>
-    <row r="59" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A59" s="5" t="s">
         <v>23</v>
       </c>
@@ -58128,11 +57929,8 @@
       <c r="AF59">
         <v>-3381.2003502735702</v>
       </c>
-      <c r="AG59">
-        <v>-2.1055296360161355</v>
-      </c>
     </row>
-    <row r="60" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A60" s="5" t="s">
         <v>28</v>
       </c>
@@ -58231,11 +58029,8 @@
       <c r="AF60">
         <v>-455.37867480526484</v>
       </c>
-      <c r="AG60">
-        <v>-0.22530673999336739</v>
-      </c>
     </row>
-    <row r="61" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A61" s="5" t="s">
         <v>42</v>
       </c>
@@ -58334,11 +58129,8 @@
       <c r="AF61">
         <v>-794.65795458607499</v>
       </c>
-      <c r="AG61">
-        <v>-0.74853437214954699</v>
-      </c>
     </row>
-    <row r="62" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A62" s="5" t="s">
         <v>28</v>
       </c>
@@ -58437,11 +58229,8 @@
       <c r="AF62">
         <v>4467.2882609118105</v>
       </c>
-      <c r="AG62">
-        <v>0.50397628054162635</v>
-      </c>
     </row>
-    <row r="63" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A63" s="5" t="s">
         <v>23</v>
       </c>
@@ -58540,11 +58329,8 @@
       <c r="AF63">
         <v>1905.9420434030453</v>
       </c>
-      <c r="AG63">
-        <v>0.27680158462470056</v>
-      </c>
     </row>
-    <row r="64" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A64" s="5" t="s">
         <v>42</v>
       </c>
@@ -58643,11 +58429,8 @@
       <c r="AF64">
         <v>-261.30720980088472</v>
       </c>
-      <c r="AG64">
-        <v>-6.7006198335958098E-2</v>
-      </c>
     </row>
-    <row r="65" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A65" s="5" t="s">
         <v>28</v>
       </c>
@@ -58746,11 +58529,8 @@
       <c r="AF65">
         <v>139.32991140944432</v>
       </c>
-      <c r="AG65">
-        <v>3.2729992019969643E-2</v>
-      </c>
     </row>
-    <row r="66" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A66" s="5" t="s">
         <v>28</v>
       </c>
@@ -58849,11 +58629,8 @@
       <c r="AF66">
         <v>7074.8391986331808</v>
       </c>
-      <c r="AG66">
-        <v>0.83639488007908713</v>
-      </c>
     </row>
-    <row r="67" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A67" s="5" t="s">
         <v>28</v>
       </c>
@@ -58952,11 +58729,8 @@
       <c r="AF67">
         <v>5653.9175721421543</v>
       </c>
-      <c r="AG67">
-        <v>0.67674470581570922</v>
-      </c>
     </row>
-    <row r="68" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A68" s="5" t="s">
         <v>28</v>
       </c>
@@ -59055,11 +58829,8 @@
       <c r="AF68">
         <v>4931.2907286880654</v>
       </c>
-      <c r="AG68">
-        <v>0.58932299062965676</v>
-      </c>
     </row>
-    <row r="69" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A69" s="5" t="s">
         <v>28</v>
       </c>
@@ -59158,11 +58929,8 @@
       <c r="AF69">
         <v>6737.5930067034897</v>
       </c>
-      <c r="AG69">
-        <v>0.7111818284054775</v>
-      </c>
     </row>
-    <row r="70" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A70" s="5" t="s">
         <v>23</v>
       </c>
@@ -59261,11 +59029,8 @@
       <c r="AF70">
         <v>1945.9858539854349</v>
       </c>
-      <c r="AG70">
-        <v>0.54813130257483544</v>
-      </c>
     </row>
-    <row r="71" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A71" s="5" t="s">
         <v>28</v>
       </c>
@@ -59364,11 +59129,8 @@
       <c r="AF71">
         <v>-1336.9534948077651</v>
       </c>
-      <c r="AG71">
-        <v>-0.7629353594127285</v>
-      </c>
     </row>
-    <row r="72" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A72" s="5" t="s">
         <v>23</v>
       </c>
@@ -59467,11 +59229,8 @@
       <c r="AF72">
         <v>5516.3564716128658</v>
       </c>
-      <c r="AG72">
-        <v>0.78637841141239195</v>
-      </c>
     </row>
-    <row r="73" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A73" s="5" t="s">
         <v>42</v>
       </c>
@@ -59570,11 +59329,8 @@
       <c r="AF73">
         <v>5230.44430728524</v>
       </c>
-      <c r="AG73">
-        <v>0.6393922710842932</v>
-      </c>
     </row>
-    <row r="74" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A74" s="5" t="s">
         <v>42</v>
       </c>
@@ -59673,11 +59429,8 @@
       <c r="AF74">
         <v>1018.0573415498598</v>
       </c>
-      <c r="AG74">
-        <v>0.38663508518602618</v>
-      </c>
     </row>
-    <row r="75" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A75" s="5" t="s">
         <v>42</v>
       </c>
@@ -59776,11 +59529,8 @@
       <c r="AF75">
         <v>5896.0429707718304</v>
       </c>
-      <c r="AG75">
-        <v>0.74530745203070226</v>
-      </c>
     </row>
-    <row r="76" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A76" s="5" t="s">
         <v>23</v>
       </c>
@@ -59879,11 +59629,8 @@
       <c r="AF76">
         <v>4532.6391122915948</v>
       </c>
-      <c r="AG76">
-        <v>0.79381480510701918</v>
-      </c>
     </row>
-    <row r="77" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A77" s="5" t="s">
         <v>28</v>
       </c>
@@ -59982,11 +59729,8 @@
       <c r="AF77">
         <v>-2511.3313514564752</v>
       </c>
-      <c r="AG77">
-        <v>-1.3293983702084542</v>
-      </c>
     </row>
-    <row r="78" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A78" s="5" t="s">
         <v>23</v>
       </c>
@@ -60085,11 +59829,8 @@
       <c r="AF78">
         <v>1516.0800735193343</v>
       </c>
-      <c r="AG78">
-        <v>0.28452948477868067</v>
-      </c>
     </row>
-    <row r="79" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A79" s="5" t="s">
         <v>23</v>
       </c>
@@ -60188,11 +59929,8 @@
       <c r="AF79">
         <v>-2133.4429810168203</v>
       </c>
-      <c r="AG79">
-        <v>-0.85895691552936393</v>
-      </c>
     </row>
-    <row r="80" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A80" s="5" t="s">
         <v>23</v>
       </c>
@@ -60291,11 +60029,8 @@
       <c r="AF80">
         <v>-2062.2135360243001</v>
       </c>
-      <c r="AG80">
-        <v>-1.595574377792961</v>
-      </c>
     </row>
-    <row r="81" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A81" s="5" t="s">
         <v>23</v>
       </c>
@@ -60394,11 +60129,8 @@
       <c r="AF81">
         <v>4499.0004191961652</v>
       </c>
-      <c r="AG81">
-        <v>0.57030780090898203</v>
-      </c>
     </row>
-    <row r="82" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A82" s="5" t="s">
         <v>28</v>
       </c>
@@ -60497,11 +60229,8 @@
       <c r="AF82">
         <v>6749.4929974222396</v>
       </c>
-      <c r="AG82">
-        <v>0.78013734970563209</v>
-      </c>
     </row>
-    <row r="83" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A83" s="5" t="s">
         <v>23</v>
       </c>
@@ -60600,11 +60329,8 @@
       <c r="AF83">
         <v>1997.8752445913451</v>
       </c>
-      <c r="AG83">
-        <v>0.45567674904251682</v>
-      </c>
     </row>
-    <row r="84" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A84" s="5" t="s">
         <v>28</v>
       </c>
@@ -60703,11 +60429,8 @@
       <c r="AF84">
         <v>-1319.4586269897995</v>
       </c>
-      <c r="AG84">
-        <v>-0.4482797973004552</v>
-      </c>
     </row>
-    <row r="85" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A85" s="5" t="s">
         <v>23</v>
       </c>
@@ -60806,11 +60529,8 @@
       <c r="AF85">
         <v>1492.0897918925202</v>
       </c>
-      <c r="AG85">
-        <v>0.61867396128387031</v>
-      </c>
     </row>
-    <row r="86" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A86" s="5" t="s">
         <v>23</v>
       </c>
@@ -60909,11 +60629,8 @@
       <c r="AF86">
         <v>1020.4301207139749</v>
       </c>
-      <c r="AG86">
-        <v>0.49818632662890167</v>
-      </c>
     </row>
-    <row r="87" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A87" s="5" t="s">
         <v>42</v>
       </c>
@@ -61012,11 +60729,8 @@
       <c r="AF87">
         <v>5269.7579681233856</v>
       </c>
-      <c r="AG87">
-        <v>0.60679248829724419</v>
-      </c>
     </row>
-    <row r="88" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A88" s="5" t="s">
         <v>28</v>
       </c>
@@ -61115,11 +60829,8 @@
       <c r="AF88">
         <v>-2800.924859949635</v>
       </c>
-      <c r="AG88">
-        <v>-2.277932088703114</v>
-      </c>
     </row>
-    <row r="89" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A89" s="5" t="s">
         <v>23</v>
       </c>
@@ -61218,11 +60929,8 @@
       <c r="AF89">
         <v>2841.1669723906448</v>
       </c>
-      <c r="AG89">
-        <v>0.55341873994586754</v>
-      </c>
     </row>
-    <row r="90" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A90" s="5" t="s">
         <v>42</v>
       </c>
@@ -61321,11 +61029,8 @@
       <c r="AF90">
         <v>8294.2781203791692</v>
       </c>
-      <c r="AG90">
-        <v>0.87819001210870462</v>
-      </c>
     </row>
-    <row r="91" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A91" s="5" t="s">
         <v>42</v>
       </c>
@@ -61424,11 +61129,8 @@
       <c r="AF91">
         <v>3597.3975370347953</v>
       </c>
-      <c r="AG91">
-        <v>0.60718823269302624</v>
-      </c>
     </row>
-    <row r="92" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A92" s="5" t="s">
         <v>28</v>
       </c>
@@ -61527,11 +61229,8 @@
       <c r="AF92">
         <v>9040.8118941234898</v>
       </c>
-      <c r="AG92">
-        <v>0.94247443393788521</v>
-      </c>
     </row>
-    <row r="93" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A93" s="5" t="s">
         <v>42</v>
       </c>
@@ -61630,11 +61329,8 @@
       <c r="AF93">
         <v>-1333.1581792525747</v>
       </c>
-      <c r="AG93">
-        <v>-0.68889701282838434</v>
-      </c>
     </row>
-    <row r="94" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A94" s="5" t="s">
         <v>42</v>
       </c>
@@ -61733,11 +61429,8 @@
       <c r="AF94">
         <v>-2883.7618201271844</v>
       </c>
-      <c r="AG94">
-        <v>-1.3731350711903192</v>
-      </c>
     </row>
-    <row r="95" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A95" s="5" t="s">
         <v>23</v>
       </c>
@@ -61836,11 +61529,8 @@
       <c r="AF95">
         <v>165.75389360364534</v>
       </c>
-      <c r="AG95">
-        <v>3.6578941509346805E-2</v>
-      </c>
     </row>
-    <row r="96" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A96" s="5" t="s">
         <v>42</v>
       </c>
@@ -61939,11 +61629,8 @@
       <c r="AF96">
         <v>4710.0709441519157</v>
       </c>
-      <c r="AG96">
-        <v>0.5970915381791515</v>
-      </c>
     </row>
-    <row r="97" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A97" s="5" t="s">
         <v>23</v>
       </c>
@@ -62042,11 +61729,8 @@
       <c r="AF97">
         <v>6348.0479130057856</v>
       </c>
-      <c r="AG97">
-        <v>0.85942798934522224</v>
-      </c>
     </row>
-    <row r="98" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A98" s="5" t="s">
         <v>42</v>
       </c>
@@ -62145,11 +61829,8 @@
       <c r="AF98">
         <v>5287.4685726194703</v>
       </c>
-      <c r="AG98">
-        <v>0.68682473799369803</v>
-      </c>
     </row>
-    <row r="99" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A99" s="5" t="s">
         <v>23</v>
       </c>
@@ -62248,11 +61929,8 @@
       <c r="AF99">
         <v>2752.9555628279195</v>
       </c>
-      <c r="AG99">
-        <v>0.62983484412270874</v>
-      </c>
     </row>
-    <row r="100" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A100" s="5" t="s">
         <v>28</v>
       </c>
@@ -62351,11 +62029,8 @@
       <c r="AF100">
         <v>7204.6781105041891</v>
       </c>
-      <c r="AG100">
-        <v>0.84502911083188392</v>
-      </c>
     </row>
-    <row r="101" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A101" s="5" t="s">
         <v>23</v>
       </c>
@@ -62453,9 +62128,6 @@
       </c>
       <c r="AF101">
         <v>7622.3144611312364</v>
-      </c>
-      <c r="AG101">
-        <v>0.82984869363392089</v>
       </c>
     </row>
   </sheetData>
@@ -62509,8 +62181,8 @@
         <v>312981.92765893816</v>
       </c>
       <c r="D4" s="13">
-        <f>AVERAGE(supply_chain_clean_dataset!AG:AG)</f>
-        <v>0.30002950865390327</v>
+        <f>SUM(supply_chain_clean_dataset!AF2:AF101)/SUM(supply_chain_clean_dataset!I2:I101)</f>
+        <v>0.54186169766167003</v>
       </c>
       <c r="E4">
         <f>SUM(supplychain_dataset!E:E)</f>
@@ -62557,7 +62229,7 @@
         <v>158</v>
       </c>
       <c r="AJ2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AK2"/>
     </row>
@@ -62642,7 +62314,7 @@
     </row>
     <row r="14" spans="2:37" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C14"/>
       <c r="D14"/>
@@ -62725,7 +62397,7 @@
         <v>158</v>
       </c>
       <c r="AI25" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AJ25"/>
     </row>
@@ -62822,7 +62494,7 @@
         <v>158</v>
       </c>
       <c r="AD36" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AE36"/>
       <c r="AH36"/>
@@ -62977,7 +62649,7 @@
         <v>158</v>
       </c>
       <c r="B2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -63139,7 +62811,7 @@
         <v>158</v>
       </c>
       <c r="B27" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C27" t="s">
         <v>161</v>
